--- a/www/download/IND.value.m.mv.zdW13.xlsx
+++ b/www/download/IND.value.m.mv.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>936617.938892092</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>876812.357568678</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>866118.934939115</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>980214.004921368</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>1002200.59260862</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1028361.11712778</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1069962.47385415</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>1012180.36160638</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>825922.77290717</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>753010.827659363</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>681934.295401833</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>656206.851679447</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>579338.233956856</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>548575.025520351</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>570819.871533172</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>791876.980543004</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>848136.09633972</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>868893.008922009</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>881049.190142964</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>914020.072972021</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1056139.89425175</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.051</t>
+          <t>1051296.41281004</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.957</t>
+          <t>957012.750003494</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>811355.406003353</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>729290.636427662</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>689103.760990081</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>683581.807196036</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>596327.451080794</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>544628.919613984</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>539365.248584082</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>689127.342842912</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>679862.3486297</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>726670.584652277</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>725475.546010919</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>760306.29489221</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>830151.502029178</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>814806.665790319</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>767330.846601829</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>686756.472145855</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>629035.038350095</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>597012.009445448</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>572414.436728041</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>517641.103883208</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>527865.895553514</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>485544.550257112</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.514</t>
+          <t>8514297.85252811</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.074</t>
+          <t>8074413.3508796</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.493</t>
+          <t>9492952.42907177</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.533</t>
+          <t>8532605.59845383</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.599</t>
+          <t>7599459.08579626</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7319890.57516607</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.504</t>
+          <t>6503745.56576759</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.663</t>
+          <t>5663222.10413044</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.279</t>
+          <t>4278721.91622585</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.655</t>
+          <t>3655451.66738627</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3.387</t>
+          <t>3387391.95792091</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3.055</t>
+          <t>3054773.41060673</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2449566.04412119</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.096</t>
+          <t>2095527.04882165</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2189777.18715877</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.633</t>
+          <t>3633379.16347672</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.403</t>
+          <t>3403363.66888217</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.308</t>
+          <t>3307949.30233175</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.375</t>
+          <t>3374733.69921447</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.867</t>
+          <t>4867180.45075702</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.316</t>
+          <t>4316444.79225566</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.843</t>
+          <t>4843197.20795006</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.218</t>
+          <t>5218471.22906656</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.829</t>
+          <t>4828608.72139175</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.252</t>
+          <t>4251757.90478518</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3490459.21160702</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.956</t>
+          <t>2955839.00762329</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.425</t>
+          <t>2424826.85238615</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.041</t>
+          <t>2041052.74761684</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>2105389.10206426</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>974523.957686296</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>940990.968270188</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.907</t>
+          <t>906585.357391117</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>952526.424634674</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>934091.499408965</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>910306.08561155</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.982</t>
+          <t>981921.757782813</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>900767.102131251</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>816252.627575255</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>786894.795741854</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>762788.550630965</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>699837.784503609</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>614454.689972241</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>589230.439511011</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>598107.496368013</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21.989</t>
+          <t>21988632.091818</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19.314</t>
+          <t>19314384.7102821</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.383</t>
+          <t>17382821.3757508</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>16.744</t>
+          <t>16743905.7190897</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15.464</t>
+          <t>15463944.1399535</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>13.843</t>
+          <t>13843350.5649269</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12.836</t>
+          <t>12836108.6142481</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.952</t>
+          <t>11951977.1555471</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11.347</t>
+          <t>11346858.1547219</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10379855.8001387</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9.289</t>
+          <t>9288698.38322579</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8.083</t>
+          <t>8083002.99752156</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6.588</t>
+          <t>6588092.75967611</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5.309</t>
+          <t>5308583.39363379</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5.056</t>
+          <t>5056048.69221435</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.716</t>
+          <t>1716454.27564987</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.775</t>
+          <t>1774797.12371234</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>1748376.28752403</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.726</t>
+          <t>1725988.22360881</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.913</t>
+          <t>1912500.99375705</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.967</t>
+          <t>1967066.34921224</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>2014688.33859553</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>1855717.09090577</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1604567.46310259</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1403570.74425474</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1172536.71881773</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>1091930.33655859</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>900411.364938282</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1060895.51128975</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>801046.308319572</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>3025495.44736765</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.778</t>
+          <t>2777531.35584285</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.967</t>
+          <t>2966886.52192307</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2.791</t>
+          <t>2791148.28809635</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.838</t>
+          <t>2837966.65974445</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.841</t>
+          <t>2841482.48487325</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.621</t>
+          <t>2620909.73082346</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.262</t>
+          <t>2262267.28594055</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.836</t>
+          <t>1836469.6151672</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1552453.34777911</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>1436380.06708275</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.314</t>
+          <t>1314356.53055468</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>1098316.90127007</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>940072.115632993</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1010671.31872134</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>694473.424987196</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>671653.385582668</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>724189.465736388</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>739917.097411536</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>768905.688228584</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>886911.53903242</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>853065.99585364</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>793611.712230884</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>709127.957196003</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>674860.892978538</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>654160.230866315</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>637967.054500793</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>577977.026624917</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>516994.734209257</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>530168.285261084</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>769079.53603549</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>755682.776750963</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>785516.417169389</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>797051.322674544</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>762176.439359926</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>813059.958739669</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>850622.201768342</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>777139.261537298</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>684872.635492822</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>626302.257884066</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>588671.420590595</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>542941.917748168</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>479064.606808268</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>453756.904064174</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>460408.896353496</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>937458.127660226</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>916318.396147125</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>976472.291143053</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1000677.70053008</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.085</t>
+          <t>1084577.14705849</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1221942.0477034</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1174021.64508253</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1081054.85847517</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>884787.737932615</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>793213.294554848</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>748940.903377579</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>718349.718220777</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>631257.759643419</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>574536.411029024</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>534730.467043208</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5919673.1480188</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.938</t>
+          <t>4937650.23355795</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.065</t>
+          <t>5065248.14579796</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>4199050.16109103</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.725</t>
+          <t>3725408.77591799</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.778</t>
+          <t>3778480.36747106</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.648</t>
+          <t>3648411.81132933</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.262</t>
+          <t>3261766.61433326</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.648</t>
+          <t>2648240.50836254</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.383</t>
+          <t>2382596.72428108</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.983</t>
+          <t>1982657.7520599</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1719559.45066634</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1317164.5092353</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1171767.77231059</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>1237099.32250003</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>781909.423983142</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>809292.203337012</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>838183.34320226</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>865949.96785572</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>961400.069440948</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>996672.27140039</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>932432.151021841</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>878740.718405353</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>775214.591212379</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>681019.327437055</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>667549.76674189</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>626269.546110974</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>529805.01575407</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>506930.797123204</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>470435.723810451</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>706527.342377521</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>700072.482065542</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>712432.698265049</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>714779.4197082</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>733768.793778022</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810668.761381886</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>804795.931452157</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>751952.536596088</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>648145.221371925</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>587853.581458747</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>567400.86138963</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>539621.98176092</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>476871.07643001</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>439591.26590407</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>421418.037826931</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>877842.465989035</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>858124.170359981</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>771228.689218102</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>736172.088512064</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>739115.418680026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>763370.615065268</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>778916.496328898</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>714168.849777293</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>644925.460077679</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>577876.221759816</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>548451.967297735</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>522591.552112589</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>455838.963823527</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456676.021869083</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.509</t>
+          <t>509390.547131206</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1625197.30512454</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1599533.65744547</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1649252.27070955</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>1691655.92387626</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.673</t>
+          <t>1673099.24521126</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1951931.73951894</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.788</t>
+          <t>1788072.75974648</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>1600665.5060998</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1271908.81387266</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.107</t>
+          <t>1106608.73716756</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1026522.00129774</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1021525.62193781</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>898529.488099666</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>785961.38674265</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>826293.247382604</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.446</t>
+          <t>3445502.84390176</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.381</t>
+          <t>3381498.27282281</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.313</t>
+          <t>3313383.07712632</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.319</t>
+          <t>3318706.40328286</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.488</t>
+          <t>3488460.78820877</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.577</t>
+          <t>3576922.90614073</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.061</t>
+          <t>3060648.39110345</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.652</t>
+          <t>2651661.47171454</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.157</t>
+          <t>2157296.69932171</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.687</t>
+          <t>1686516.96513784</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>1562301.24469265</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1493657.58670378</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>1276114.55442353</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>1018151.38029736</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>1212664.31129044</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10.754</t>
+          <t>10753501.4266537</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9699846.89615236</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9.371</t>
+          <t>9370663.89417589</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23.283</t>
+          <t>23283307.6745926</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15.603</t>
+          <t>15602841.4415583</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>13.727</t>
+          <t>13726527.659575</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14.258</t>
+          <t>14257556.1637773</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12.573</t>
+          <t>12572765.2729289</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>10.747</t>
+          <t>10746518.6654788</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>10.665</t>
+          <t>10664873.1853655</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>8.985</t>
+          <t>8984962.31999114</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6.329</t>
+          <t>6328671.97699954</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>5.385</t>
+          <t>5385225.78914899</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.678</t>
+          <t>4677890.004523</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.613</t>
+          <t>4612933.21595438</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>27.173</t>
+          <t>27173473.6559135</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26.564</t>
+          <t>26563975.5215517</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24.786</t>
+          <t>24785868.5307946</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24599678.0315087</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>23.677</t>
+          <t>23677152.6047973</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>24.581</t>
+          <t>24581022.7549681</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25.933</t>
+          <t>25933245.8918477</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>25.743</t>
+          <t>25743010.5646163</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>23.821</t>
+          <t>23821123.7530925</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>21.582</t>
+          <t>21582221.3690786</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>18.862</t>
+          <t>18861927.9193614</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>16.575</t>
+          <t>16574718.2493782</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>12.838</t>
+          <t>12838178.6806421</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>12.238</t>
+          <t>12237921.4444674</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>12.336</t>
+          <t>12335561.1009341</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>996921.554066081</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>949209.90348852</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>892179.636881848</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>876138.705821066</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>890386.794684557</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>952881.76115869</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>934036.475827283</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>832340.517095474</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>685035.125363303</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630827.786763452</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>605365.628036086</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>554429.217084726</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>510938.285728088</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>503639.352331626</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>555135.685590988</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>928272.387123979</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>853532.491437212</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>850848.244836127</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>860259.345923799</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>901427.10686922</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>1005763.79652802</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>998567.542853172</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>929121.336533884</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>796582.634737724</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>725618.163318066</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>690499.041051795</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>697557.026853225</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>605655.565839726</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>551522.066538358</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>546844.835696312</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>781430.824635337</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>851289.208238293</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>891113.634861395</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>897198.953390166</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>830226.980379748</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810627.757077941</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>898678.337280818</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>901924.71455178</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>863722.348515726</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>822954.976090034</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>809181.936875171</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>854555.273741268</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>808053.624616099</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>723153.597440644</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>648172.492746596</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>2479110.09314138</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.297</t>
+          <t>2297026.4839153</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2.401</t>
+          <t>2400627.98119408</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2.853</t>
+          <t>2853238.05490836</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.506</t>
+          <t>2505874.64099591</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>2398173.62915008</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2.557</t>
+          <t>2556766.63087169</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2.343</t>
+          <t>2342978.25182465</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.173</t>
+          <t>2172698.59152243</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.001</t>
+          <t>2000541.48055782</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1650448.10980798</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>1506875.71320282</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1343543.60016787</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.361</t>
+          <t>1360977.34338344</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1427891.78461645</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7.026</t>
+          <t>7025953.64037786</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.727</t>
+          <t>5726733.65375848</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4.797</t>
+          <t>4796919.23785121</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4.469</t>
+          <t>4469483.56703429</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.539</t>
+          <t>4539484.74308696</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.428</t>
+          <t>4428280.35225316</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4.036</t>
+          <t>4035894.45416913</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3.586</t>
+          <t>3585829.74870999</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2.923</t>
+          <t>2922920.64572953</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2.278</t>
+          <t>2277547.50934983</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2.064</t>
+          <t>2063594.14705121</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1800003.28174383</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1476252.91727832</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1253266.43648018</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1440121.41395777</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>602596.800592018</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545392.457641368</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>531491.52695766</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>551945.25262103</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>517108.013370629</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>614135.869063742</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>564342.78259278</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>531981.673384085</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>485776.745867417</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>442855.708325067</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>438339.393733465</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>416344.636700038</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>340305.49788756</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308341.377361198</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>354033.889298001</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5.678</t>
+          <t>5677842.87422806</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.775</t>
+          <t>4774821.75203519</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4.221</t>
+          <t>4221237.84598046</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3969568.7610385</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.958</t>
+          <t>3957584.96345458</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.494</t>
+          <t>3494438.37519384</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.167</t>
+          <t>3167020.16013892</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3.001</t>
+          <t>3001014.15291607</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.602</t>
+          <t>2602446.45499631</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2.171</t>
+          <t>2171116.12203914</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1960234.46263358</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1599364.22260183</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1.261</t>
+          <t>1260879.52946497</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1057708.27597962</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1.036</t>
+          <t>1035855.44741</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4010322.43793363</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.587</t>
+          <t>3587333.11794856</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.007</t>
+          <t>3007199.42860562</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2.966</t>
+          <t>2965927.87013543</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.807</t>
+          <t>2806592.69756975</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.532</t>
+          <t>2531871.47508773</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2460373.49609795</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.378</t>
+          <t>2377521.9788378</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.514</t>
+          <t>2513572.46726485</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.471</t>
+          <t>2471443.81517182</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.211</t>
+          <t>2210783.08425682</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2010037.37604423</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>1855143.50889187</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.888</t>
+          <t>1887823.52097597</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.261</t>
+          <t>2261492.60955318</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1569827.42030627</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.549</t>
+          <t>1548852.13142113</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1439472.67686535</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1420092.62077226</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>1525612.3077388</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1619371.83825741</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1475970.04435535</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.456</t>
+          <t>1456288.4643437</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1.232</t>
+          <t>1232208.08677077</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1078276.98336347</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>961033.177242223</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.982</t>
+          <t>981517.714744975</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>839387.745004101</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>769288.340796326</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>782604.49515547</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>877185.313693907</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>909124.801409113</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>920045.859381407</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>990256.998498152</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>1048336.4201723</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.096</t>
+          <t>1096086.56388698</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1098540.798173</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>931613.891412521</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>875035.847069893</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>787692.439210284</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>766121.7772239</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>718858.092154892</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>636346.018437718</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>604432.561027847</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>614827.790500254</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>3875757.2255876</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.566</t>
+          <t>3566097.13744276</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.563</t>
+          <t>3562878.60390472</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3.346</t>
+          <t>3346442.81463482</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.471</t>
+          <t>3470501.84280466</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.349</t>
+          <t>3348523.13337227</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.821</t>
+          <t>2821178.87942363</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.601</t>
+          <t>2600715.12376493</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.321</t>
+          <t>2320892.31641414</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.952</t>
+          <t>1951935.67419759</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>1736516.8676242</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1578274.08281073</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1335359.22793063</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.127</t>
+          <t>1126517.27539428</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1320722.67710185</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1787086.83584105</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>1688780.99886108</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.713</t>
+          <t>1713273.5160598</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.744</t>
+          <t>1744368.64171925</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.759</t>
+          <t>1758880.35282063</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1970127.05948564</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1960008.18283186</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.792</t>
+          <t>1791548.6303491</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1492269.52325992</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1320309.24912697</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>1243101.42573768</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1.142</t>
+          <t>1142312.13378074</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1012587.31451661</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>948102.222895165</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>912817.102582874</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>8.869</t>
+          <t>8868649.05285987</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.444</t>
+          <t>8443595.35652388</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8.303</t>
+          <t>8302678.40077254</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>7.438</t>
+          <t>7437592.43592979</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>9.331</t>
+          <t>9330780.79267895</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8799918.49540972</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7.687</t>
+          <t>7687320.08998008</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6.582</t>
+          <t>6581536.06557816</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5.185</t>
+          <t>5184923.07376198</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>3.883</t>
+          <t>3882556.3213803</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>3.157</t>
+          <t>3157092.17135043</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2.686</t>
+          <t>2685779.4396179</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2.009</t>
+          <t>2008719.70581647</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1.689</t>
+          <t>1689134.03133919</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2.022</t>
+          <t>2021677.08488462</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9.513</t>
+          <t>9513167.02455</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7.279</t>
+          <t>7279396.76812045</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6749947.33366264</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>8.303</t>
+          <t>8303278.23936524</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14.016</t>
+          <t>14015817.0097614</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11.304</t>
+          <t>11304392.271654</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9.454</t>
+          <t>9454134.34007112</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8.465</t>
+          <t>8464675.39672311</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>7190099.19933882</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5.321</t>
+          <t>5320968.42740175</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>4.345</t>
+          <t>4345172.48663384</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>3.386</t>
+          <t>3386296.80479921</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.674</t>
+          <t>2674082.76979418</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.134</t>
+          <t>2133778.71576944</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.719</t>
+          <t>2718982.83576655</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.799</t>
+          <t>3799118.11028201</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.501</t>
+          <t>3501436.50080408</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.322</t>
+          <t>3322007.74490434</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3.033</t>
+          <t>3033054.21606891</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.343</t>
+          <t>3343085.4286927</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3.271</t>
+          <t>3270792.34548109</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.057</t>
+          <t>3056579.00456522</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>2577722.52375659</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1969914.83701961</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>1719016.74324886</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1604809.28552561</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1472862.46585231</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.212</t>
+          <t>1212312.6121721</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1397782.6619214</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.549</t>
+          <t>1548881.54656045</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.901</t>
+          <t>1901247.93521574</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.853</t>
+          <t>1853240.19948715</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>1795454.92276481</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.765</t>
+          <t>1764502.67971186</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>1842464.44044857</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.988</t>
+          <t>1988392.8807056</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.984</t>
+          <t>1983798.27437884</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>1808618.80232487</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>1600783.87205098</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1361917.88336503</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1250512.59000006</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>1183265.22931054</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>983378.26112974</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>955724.471511372</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1010093.74663068</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>816191.198823022</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>717758.811742537</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>740670.899583202</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>768012.028593623</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>775795.73803652</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>840009.256681119</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>858470.512740202</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>773967.455103683</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>672630.973752934</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>599746.12093096</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>586719.49962465</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>543829.462874556</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>487170.950731641</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>451781.460145725</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>451869.086771701</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.017</t>
+          <t>3016731.88110234</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.936</t>
+          <t>2935719.57325736</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.879</t>
+          <t>2878887.37314077</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2749577.10767677</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.964</t>
+          <t>2963552.21651461</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2.763</t>
+          <t>2763322.09757488</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.504</t>
+          <t>3503614.35070554</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>3168814.86969296</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2.485</t>
+          <t>2485064.12113066</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>2087545.02122466</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1.773</t>
+          <t>1773334.6674467</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1629422.17081586</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.342</t>
+          <t>1342020.16427978</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>1184643.95821062</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.283</t>
+          <t>1283164.79346374</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>2294287.3462653</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2199959.52390997</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.133</t>
+          <t>2133420.78450566</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.321</t>
+          <t>2320802.00253995</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.164</t>
+          <t>2163819.00224623</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2.172</t>
+          <t>2172109.32949817</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2.284</t>
+          <t>2284265.88332309</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2.331</t>
+          <t>2330839.26314775</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2.292</t>
+          <t>2291532.94362504</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2.223</t>
+          <t>2222901.21114845</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2.028</t>
+          <t>2028474.55350444</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1.946</t>
+          <t>1945746.25662361</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>1.823</t>
+          <t>1822502.91745188</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>1732601.96676253</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.688</t>
+          <t>1687568.94517489</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>883476.415030806</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>842130.156678833</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>811572.625878872</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>804870.691290716</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>813665.365069025</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>826093.356273295</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>792635.921650352</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>770741.967442742</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>742849.869319694</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>730389.254610108</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>714400.826314779</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>689939.452870391</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>627177.852893502</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>598901.471521899</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>565767.992392605</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>7.667</t>
+          <t>7667082.56815636</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7.567</t>
+          <t>7567208.77237378</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7.598</t>
+          <t>7597599.8256853</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>8019840.00449013</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>8090189.80258283</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8.255</t>
+          <t>8255191.56342051</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8.763</t>
+          <t>8762585.00997788</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8.758</t>
+          <t>8758129.13102928</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8.399</t>
+          <t>8398985.08536099</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>7.823</t>
+          <t>7823398.04182931</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>7.102</t>
+          <t>7101867.06425462</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6510479.8558474</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>5.713</t>
+          <t>5712654.30426432</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>4.938</t>
+          <t>4937908.911404</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>5.419</t>
+          <t>5419239.85193627</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>165.327</t>
+          <t>165327302.691262</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>152.223</t>
+          <t>152222579.776676</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>146.819</t>
+          <t>146819220.730122</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>158.801</t>
+          <t>158801043.477381</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>157.6</t>
+          <t>157599762.862108</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>151.711</t>
+          <t>151711207.193665</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>148.173</t>
+          <t>148173207.378942</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>137.933</t>
+          <t>137933407.251171</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>121.528</t>
+          <t>121527619.955525</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>107.935</t>
+          <t>107934822.25228</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>95.397</t>
+          <t>95397453.5387183</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>83.746</t>
+          <t>83745567.7291869</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>69.529</t>
+          <t>69529475.2462159</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>62.674</t>
+          <t>62673639.2389246</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>65.116</t>
+          <t>65115639.0384998</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
